--- a/questions.xlsx
+++ b/questions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -45,9 +45,6 @@
     <t>CorrectAnswer</t>
   </si>
   <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
     <t>Which number comes next: 2, 4, 8, 16, ?</t>
   </si>
   <si>
@@ -55,6 +52,39 @@
   </si>
   <si>
     <t>Solve for x: 3x + 5 = 20</t>
+  </si>
+  <si>
+    <t>Verbal</t>
+  </si>
+  <si>
+    <t>Non-Verbal</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>General Science</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Urdu</t>
+  </si>
+  <si>
+    <t>I am Ahsan</t>
+  </si>
+  <si>
+    <t>who are you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sun is round </t>
+  </si>
+  <si>
+    <t>x+y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am good </t>
   </si>
 </sst>
 </file>
@@ -372,15 +402,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -414,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -440,10 +471,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -459,6 +490,130 @@
       </c>
       <c r="H3">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1812,19 +1812,19 @@
     <t>Q50: فعل ماضی کس زمانو کو ظاہر کرتا ہے؟</t>
   </si>
   <si>
-    <t>OptionA</t>
-  </si>
-  <si>
-    <t>OptionB</t>
-  </si>
-  <si>
-    <t>OptionC</t>
-  </si>
-  <si>
-    <t>OptionD</t>
-  </si>
-  <si>
     <t>CorrectAnswer</t>
+  </si>
+  <si>
+    <t>Option D</t>
+  </si>
+  <si>
+    <t>Option C</t>
+  </si>
+  <si>
+    <t>Option B</t>
+  </si>
+  <si>
+    <t>Option A</t>
   </si>
 </sst>
 </file>
@@ -2189,19 +2189,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F1" t="s">
         <v>599</v>
       </c>
       <c r="G1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
